--- a/data/Tag.xlsx
+++ b/data/Tag.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Training\Gathering_Island\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCreation\Web\Gathering_Island\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C82DC82-6872-45AF-A35A-CC150EAB91D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E73504F-F9E1-416A-B960-01009303BEDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tag" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="382">
   <si>
     <t>id</t>
   </si>
@@ -46,226 +46,1135 @@
     <t>美食</t>
   </si>
   <si>
-    <t>啤酒</t>
-  </si>
-  <si>
-    <t>聚會</t>
-  </si>
-  <si>
-    <t>歡樂</t>
-  </si>
-  <si>
-    <t>旅遊</t>
-  </si>
-  <si>
-    <t>揪團</t>
-  </si>
-  <si>
-    <t>行程滿</t>
-  </si>
-  <si>
-    <t>戶外</t>
-  </si>
-  <si>
-    <t>耶誕</t>
-  </si>
-  <si>
-    <t>社交</t>
-  </si>
-  <si>
-    <t>可帶朋友</t>
-  </si>
-  <si>
     <t>攝影</t>
   </si>
   <si>
-    <t>展覽</t>
-  </si>
-  <si>
-    <t>輕鬆</t>
-  </si>
-  <si>
-    <t>亂晃</t>
-  </si>
-  <si>
-    <t>行走</t>
-  </si>
-  <si>
-    <t>不正經</t>
-  </si>
-  <si>
-    <t>耍廢</t>
-  </si>
-  <si>
-    <t>學習</t>
-  </si>
-  <si>
-    <t>可聊天</t>
-  </si>
-  <si>
-    <t>可偷懶</t>
-  </si>
-  <si>
     <t>AI</t>
   </si>
   <si>
-    <t>吃東西</t>
-  </si>
-  <si>
-    <t>低壓力</t>
-  </si>
-  <si>
-    <t>技術</t>
-  </si>
-  <si>
     <t>社群</t>
   </si>
   <si>
-    <t>聊天</t>
-  </si>
-  <si>
-    <t>非正式</t>
-  </si>
-  <si>
     <t>跳舞</t>
   </si>
   <si>
     <t>音樂</t>
   </si>
   <si>
-    <t>週末</t>
-  </si>
-  <si>
-    <t>派對感</t>
-  </si>
-  <si>
-    <t>知識交流</t>
-  </si>
-  <si>
     <t>手作</t>
   </si>
   <si>
-    <t>體驗</t>
-  </si>
-  <si>
-    <t>興趣</t>
-  </si>
-  <si>
-    <t>放鬆</t>
-  </si>
-  <si>
     <t>新年</t>
   </si>
   <si>
     <t>派對</t>
   </si>
   <si>
-    <t>交流</t>
-  </si>
-  <si>
-    <t>分享</t>
-  </si>
-  <si>
-    <t>夜間</t>
-  </si>
-  <si>
-    <t>入門</t>
-  </si>
-  <si>
-    <t>實作</t>
-  </si>
-  <si>
     <t>泡湯</t>
   </si>
   <si>
-    <t>佛系</t>
-  </si>
-  <si>
-    <t>春季</t>
-  </si>
-  <si>
-    <t>藝術</t>
-  </si>
-  <si>
-    <t>同行</t>
-  </si>
-  <si>
     <t>輕旅行</t>
   </si>
   <si>
-    <t>運動</t>
-  </si>
-  <si>
     <t>慢跑</t>
   </si>
   <si>
-    <t>健康</t>
-  </si>
-  <si>
-    <t>文化</t>
-  </si>
-  <si>
-    <t>原住民</t>
-  </si>
-  <si>
-    <t>參訪</t>
-  </si>
-  <si>
     <t>桌遊</t>
   </si>
   <si>
-    <t>同樂</t>
-  </si>
-  <si>
-    <t>探店</t>
-  </si>
-  <si>
-    <t>夏日</t>
-  </si>
-  <si>
-    <t>歌單</t>
-  </si>
-  <si>
     <t>時間管理</t>
   </si>
   <si>
-    <t>成長</t>
-  </si>
-  <si>
-    <t>秋季</t>
-  </si>
-  <si>
-    <t>設計</t>
-  </si>
-  <si>
-    <t>回顧</t>
-  </si>
-  <si>
-    <t>年度</t>
-  </si>
-  <si>
-    <t>心情整理</t>
-  </si>
-  <si>
-    <t>情緒交流</t>
-  </si>
-  <si>
-    <t>抒發</t>
-  </si>
-  <si>
-    <t>目標設定</t>
-  </si>
-  <si>
     <t>聚餐</t>
   </si>
   <si>
-    <t>自由</t>
-  </si>
-  <si>
-    <t>成果</t>
-  </si>
-  <si>
-    <t>無主題</t>
+    <t>瑜伽</t>
+  </si>
+  <si>
+    <t>晨間活動</t>
+  </si>
+  <si>
+    <t>海邊</t>
+  </si>
+  <si>
+    <t>啤酒節</t>
+  </si>
+  <si>
+    <t>喝酒聚會</t>
+  </si>
+  <si>
+    <t>朋友聚餐</t>
+  </si>
+  <si>
+    <t>新機制</t>
+  </si>
+  <si>
+    <t>試玩</t>
+  </si>
+  <si>
+    <t>晨跑</t>
+  </si>
+  <si>
+    <t>森林</t>
+  </si>
+  <si>
+    <t>戶外運動</t>
+  </si>
+  <si>
+    <t>花蓮旅遊</t>
+  </si>
+  <si>
+    <t>揪團出遊</t>
+  </si>
+  <si>
+    <t>行程滿檔</t>
+  </si>
+  <si>
+    <t>咖啡交流</t>
+  </si>
+  <si>
+    <t>產地分享</t>
+  </si>
+  <si>
+    <t>夜間聚會</t>
+  </si>
+  <si>
+    <t>派對遊戲</t>
+  </si>
+  <si>
+    <t>電音</t>
+  </si>
+  <si>
+    <t>音樂祭</t>
+  </si>
+  <si>
+    <t>戶外活動</t>
+  </si>
+  <si>
+    <t>聖誕節</t>
+  </si>
+  <si>
+    <t>交換禮物</t>
+  </si>
+  <si>
+    <t>公司活動</t>
+  </si>
+  <si>
+    <t>攝影展</t>
+  </si>
+  <si>
+    <t>藝文</t>
+  </si>
+  <si>
+    <t>城市散步</t>
+  </si>
+  <si>
+    <t>老街</t>
+  </si>
+  <si>
+    <t>光影</t>
+  </si>
+  <si>
+    <t>咖啡</t>
+  </si>
+  <si>
+    <t>沖煮教學</t>
+  </si>
+  <si>
+    <t>風味比較</t>
+  </si>
+  <si>
+    <t>電子音樂</t>
+  </si>
+  <si>
+    <t>夜生活</t>
+  </si>
+  <si>
+    <t>迷路冒險</t>
+  </si>
+  <si>
+    <t>朋友聚會</t>
+  </si>
+  <si>
+    <t>學習營</t>
+  </si>
+  <si>
+    <t>輕鬆學習</t>
+  </si>
+  <si>
+    <t>聊天交流</t>
+  </si>
+  <si>
+    <t>講座</t>
+  </si>
+  <si>
+    <t>科技分享</t>
+  </si>
+  <si>
+    <t>寫作</t>
+  </si>
+  <si>
+    <t>創作營</t>
+  </si>
+  <si>
+    <t>短篇小說</t>
+  </si>
+  <si>
+    <t>登山</t>
+  </si>
+  <si>
+    <t>山徑</t>
+  </si>
+  <si>
+    <t>戶外探索</t>
+  </si>
+  <si>
+    <t>開發者</t>
+  </si>
+  <si>
+    <t>技術交流</t>
+  </si>
+  <si>
+    <t>夜間活動</t>
+  </si>
+  <si>
+    <t>料理</t>
+  </si>
+  <si>
+    <t>沙灘</t>
+  </si>
+  <si>
+    <t>晚餐聚會</t>
+  </si>
+  <si>
+    <t>散步拍攝</t>
+  </si>
+  <si>
+    <t>露營</t>
+  </si>
+  <si>
+    <t>兩天一夜</t>
+  </si>
+  <si>
+    <t>山野體驗</t>
+  </si>
+  <si>
+    <t>劇本分析</t>
+  </si>
+  <si>
+    <t>讀書會</t>
+  </si>
+  <si>
+    <t>戲劇</t>
+  </si>
+  <si>
+    <t>湖畔</t>
+  </si>
+  <si>
+    <t>輕量旅行</t>
+  </si>
+  <si>
+    <t>詩歌</t>
+  </si>
+  <si>
+    <t>朗誦</t>
+  </si>
+  <si>
+    <t>藝文交流</t>
+  </si>
+  <si>
+    <t>划船</t>
+  </si>
+  <si>
+    <t>湖上活動</t>
+  </si>
+  <si>
+    <t>基礎教學</t>
+  </si>
+  <si>
+    <t>交流分享</t>
+  </si>
+  <si>
+    <t>沙灘派對</t>
+  </si>
+  <si>
+    <t>晚餐</t>
+  </si>
+  <si>
+    <t>桌棋</t>
+  </si>
+  <si>
+    <t>策略</t>
+  </si>
+  <si>
+    <t>對抗賽</t>
+  </si>
+  <si>
+    <t>戶外電影</t>
+  </si>
+  <si>
+    <t>山景</t>
+  </si>
+  <si>
+    <t>映後討論</t>
+  </si>
+  <si>
+    <t>戲劇結構</t>
+  </si>
+  <si>
+    <t>燈光演出</t>
+  </si>
+  <si>
+    <t>體驗活動</t>
+  </si>
+  <si>
+    <t>河濱</t>
+  </si>
+  <si>
+    <t>電音祭</t>
+  </si>
+  <si>
+    <t>燈光秀</t>
+  </si>
+  <si>
+    <t>社交交流</t>
+  </si>
+  <si>
+    <t>私廚</t>
+  </si>
+  <si>
+    <t>季節料理</t>
+  </si>
+  <si>
+    <t>餐會</t>
+  </si>
+  <si>
+    <t>戶外草地</t>
+  </si>
+  <si>
+    <t>冥想</t>
+  </si>
+  <si>
+    <t>創作工作坊</t>
+  </si>
+  <si>
+    <t>城市夜景</t>
+  </si>
+  <si>
+    <t>Coding</t>
+  </si>
+  <si>
+    <t>熬夜開發</t>
+  </si>
+  <si>
+    <t>工程師聚會</t>
+  </si>
+  <si>
+    <t>精品咖啡</t>
+  </si>
+  <si>
+    <t>垂直品飲</t>
+  </si>
+  <si>
+    <t>莊園豆</t>
+  </si>
+  <si>
+    <t>藝術導覽</t>
+  </si>
+  <si>
+    <t>畫廊</t>
+  </si>
+  <si>
+    <t>香檳交流</t>
+  </si>
+  <si>
+    <t>音樂分享</t>
+  </si>
+  <si>
+    <t>歌單交流</t>
+  </si>
+  <si>
+    <t>禁書討論</t>
+  </si>
+  <si>
+    <t>威士忌</t>
+  </si>
+  <si>
+    <t>品飲會</t>
+  </si>
+  <si>
+    <t>單桶原酒</t>
+  </si>
+  <si>
+    <t>策展</t>
+  </si>
+  <si>
+    <t>市集</t>
+  </si>
+  <si>
+    <t>夜跑</t>
+  </si>
+  <si>
+    <t>城市運動</t>
+  </si>
+  <si>
+    <t>10公里挑戰</t>
+  </si>
+  <si>
+    <t>深夜談心</t>
+  </si>
+  <si>
+    <t>誠實對話</t>
+  </si>
+  <si>
+    <t>策略對弈</t>
+  </si>
+  <si>
+    <t>訂製西裝</t>
+  </si>
+  <si>
+    <t>形象顧問</t>
+  </si>
+  <si>
+    <t>量身體驗</t>
+  </si>
+  <si>
+    <t>現場音樂</t>
+  </si>
+  <si>
+    <t>獨立樂團</t>
+  </si>
+  <si>
+    <t>單人旅行</t>
+  </si>
+  <si>
+    <t>生活技能</t>
+  </si>
+  <si>
+    <t>搖滾</t>
+  </si>
+  <si>
+    <t>地下室演出</t>
+  </si>
+  <si>
+    <t>攝影基礎</t>
+  </si>
+  <si>
+    <t>構圖教學</t>
+  </si>
+  <si>
+    <t>甜點手作</t>
+  </si>
+  <si>
+    <t>情緒療癒</t>
+  </si>
+  <si>
+    <t>密室逃脫</t>
+  </si>
+  <si>
+    <t>解謎</t>
+  </si>
+  <si>
+    <t>人生講座</t>
+  </si>
+  <si>
+    <t>分手療癒</t>
+  </si>
+  <si>
+    <t>天台晚宴</t>
+  </si>
+  <si>
+    <t>香檳</t>
+  </si>
+  <si>
+    <t>料理實驗</t>
+  </si>
+  <si>
+    <t>地方食材</t>
+  </si>
+  <si>
+    <t>北海道</t>
+  </si>
+  <si>
+    <t>戶外寫生</t>
+  </si>
+  <si>
+    <t>城市速寫</t>
+  </si>
+  <si>
+    <t>茶席</t>
+  </si>
+  <si>
+    <t>靜心體驗</t>
+  </si>
+  <si>
+    <t>藝術展覽</t>
+  </si>
+  <si>
+    <t>同行看展</t>
+  </si>
+  <si>
+    <t>街舞</t>
+  </si>
+  <si>
+    <t>舞蹈教學</t>
+  </si>
+  <si>
+    <t>遊艇</t>
+  </si>
+  <si>
+    <t>海上午宴</t>
+  </si>
+  <si>
+    <t>咖啡講堂</t>
+  </si>
+  <si>
+    <t>沖煮解析</t>
+  </si>
+  <si>
+    <t>海岸攝影</t>
+  </si>
+  <si>
+    <t>日出拍攝</t>
+  </si>
+  <si>
+    <t>廢墟攝影</t>
+  </si>
+  <si>
+    <t>夜拍</t>
+  </si>
+  <si>
+    <t>夜談</t>
+  </si>
+  <si>
+    <t>城市議題</t>
+  </si>
+  <si>
+    <t>哲學夜談</t>
+  </si>
+  <si>
+    <t>紅酒</t>
+  </si>
+  <si>
+    <t>攝影漫遊</t>
+  </si>
+  <si>
+    <t>城市光影</t>
+  </si>
+  <si>
+    <t>海邊晨跑</t>
+  </si>
+  <si>
+    <t>策略遊戲</t>
+  </si>
+  <si>
+    <t>一日遊</t>
+  </si>
+  <si>
+    <t>故事交流</t>
+  </si>
+  <si>
+    <t>咖啡研究</t>
+  </si>
+  <si>
+    <t>沖煮技巧</t>
+  </si>
+  <si>
+    <t>展覽規劃</t>
+  </si>
+  <si>
+    <t>夜行探索</t>
+  </si>
+  <si>
+    <t>戶外冒險</t>
+  </si>
+  <si>
+    <t>劇本讀書會</t>
+  </si>
+  <si>
+    <t>創新料理</t>
+  </si>
+  <si>
+    <t>黑膠</t>
+  </si>
+  <si>
+    <t>音響體驗</t>
+  </si>
+  <si>
+    <t>燈光互動</t>
+  </si>
+  <si>
+    <t>戶外伸展</t>
+  </si>
+  <si>
+    <t>摺紙</t>
+  </si>
+  <si>
+    <t>敘事練習</t>
+  </si>
+  <si>
+    <t>策略對抗</t>
+  </si>
+  <si>
+    <t>料理派對</t>
+  </si>
+  <si>
+    <t>沙灘晚餐</t>
+  </si>
+  <si>
+    <t>入門運動</t>
+  </si>
+  <si>
+    <t>市集策展</t>
+  </si>
+  <si>
+    <t>企劃分享</t>
+  </si>
+  <si>
+    <t>看展</t>
+  </si>
+  <si>
+    <t>花藝</t>
+  </si>
+  <si>
+    <t>設計實作</t>
+  </si>
+  <si>
+    <t>山徑健行</t>
+  </si>
+  <si>
+    <t>戶外攝影</t>
+  </si>
+  <si>
+    <t>微醺餐會</t>
+  </si>
+  <si>
+    <t>主廚晚宴</t>
+  </si>
+  <si>
+    <t>心理戰</t>
+  </si>
+  <si>
+    <t>極限對局</t>
+  </si>
+  <si>
+    <t>米其林</t>
+  </si>
+  <si>
+    <t>客座主廚</t>
+  </si>
+  <si>
+    <t>高端料理</t>
+  </si>
+  <si>
+    <t>原住民文化</t>
+  </si>
+  <si>
+    <t>文化參訪</t>
+  </si>
+  <si>
+    <t>屋頂派對</t>
+  </si>
+  <si>
+    <t>神秘活動</t>
+  </si>
+  <si>
+    <t>肖像攝影</t>
+  </si>
+  <si>
+    <t>攝影棚</t>
+  </si>
+  <si>
+    <t>專業拍攝</t>
+  </si>
+  <si>
+    <t>音樂交流</t>
+  </si>
+  <si>
+    <t>歌單分享</t>
+  </si>
+  <si>
+    <t>攝影比賽</t>
+  </si>
+  <si>
+    <t>限時挑戰</t>
+  </si>
+  <si>
+    <t>商務晚宴</t>
+  </si>
+  <si>
+    <t>高階交流</t>
+  </si>
+  <si>
+    <t>策略對戰</t>
+  </si>
+  <si>
+    <t>城市攝影</t>
+  </si>
+  <si>
+    <t>長曝光</t>
+  </si>
+  <si>
+    <t>深夜運動</t>
+  </si>
+  <si>
+    <t>美食探店</t>
+  </si>
+  <si>
+    <t>餐廳踩點</t>
+  </si>
+  <si>
+    <t>羽球</t>
+  </si>
+  <si>
+    <t>運動挑戰</t>
+  </si>
+  <si>
+    <t>松露料理</t>
+  </si>
+  <si>
+    <t>頂級食材</t>
+  </si>
+  <si>
+    <t>創業講座</t>
+  </si>
+  <si>
+    <t>新創交流</t>
+  </si>
+  <si>
+    <t>派對型桌遊</t>
+  </si>
+  <si>
+    <t>沉浸體驗</t>
+  </si>
+  <si>
+    <t>恐懼主題</t>
+  </si>
+  <si>
+    <t>郊山健行</t>
+  </si>
+  <si>
+    <t>古典音樂</t>
+  </si>
+  <si>
+    <t>弦樂四重奏</t>
+  </si>
+  <si>
+    <t>夏日派對</t>
+  </si>
+  <si>
+    <t>輕鬆聊天</t>
+  </si>
+  <si>
+    <t>登山體驗</t>
+  </si>
+  <si>
+    <t>戶外導覽</t>
+  </si>
+  <si>
+    <t>手沖技巧</t>
+  </si>
+  <si>
+    <t>划艇</t>
+  </si>
+  <si>
+    <t>海灣體驗</t>
+  </si>
+  <si>
+    <t>失戀歌單</t>
+  </si>
+  <si>
+    <t>匿名分享</t>
+  </si>
+  <si>
+    <t>香水調製</t>
+  </si>
+  <si>
+    <t>法式香氛</t>
+  </si>
+  <si>
+    <t>深夜電台</t>
+  </si>
+  <si>
+    <t>匿名對談</t>
+  </si>
+  <si>
+    <t>紅酒品鑑</t>
+  </si>
+  <si>
+    <t>垂直年份</t>
+  </si>
+  <si>
+    <t>歌單交換</t>
+  </si>
+  <si>
+    <t>設計展覽</t>
+  </si>
+  <si>
+    <t>導覽賞析</t>
+  </si>
+  <si>
+    <t>馬術體驗</t>
+  </si>
+  <si>
+    <t>一對一教學</t>
+  </si>
+  <si>
+    <t>TypeScript</t>
+  </si>
+  <si>
+    <t>程式讀書會</t>
+  </si>
+  <si>
+    <t>工程師分享</t>
+  </si>
+  <si>
+    <t>失敗故事</t>
+  </si>
+  <si>
+    <t>料理對決</t>
+  </si>
+  <si>
+    <t>團隊競賽</t>
+  </si>
+  <si>
+    <t>萬聖派對</t>
+  </si>
+  <si>
+    <t>變裝活動</t>
+  </si>
+  <si>
+    <t>萬聖節</t>
+  </si>
+  <si>
+    <t>恐怖主題</t>
+  </si>
+  <si>
+    <t>萬聖舞會</t>
+  </si>
+  <si>
+    <t>變裝舞會</t>
+  </si>
+  <si>
+    <t>Bug分享</t>
+  </si>
+  <si>
+    <t>工程師吐槽</t>
+  </si>
+  <si>
+    <t>溫泉旅行</t>
+  </si>
+  <si>
+    <t>包棟旅宿</t>
+  </si>
+  <si>
+    <t>主題晚宴</t>
+  </si>
+  <si>
+    <t>DressCode</t>
+  </si>
+  <si>
+    <t>學習成長</t>
+  </si>
+  <si>
+    <t>營火</t>
+  </si>
+  <si>
+    <t>野外露營</t>
+  </si>
+  <si>
+    <t>電影節</t>
+  </si>
+  <si>
+    <t>滑雪旅行</t>
+  </si>
+  <si>
+    <t>雪場體驗</t>
+  </si>
+  <si>
+    <t>雪地露營</t>
+  </si>
+  <si>
+    <t>慈善晚宴</t>
+  </si>
+  <si>
+    <t>黑領結</t>
+  </si>
+  <si>
+    <t>主題展覽</t>
+  </si>
+  <si>
+    <t>看展交流</t>
+  </si>
+  <si>
+    <t>跨年派對</t>
+  </si>
+  <si>
+    <t>新年反思</t>
+  </si>
+  <si>
+    <t>價值觀討論</t>
+  </si>
+  <si>
+    <t>湖畔露營</t>
+  </si>
+  <si>
+    <t>新年清算</t>
+  </si>
+  <si>
+    <t>自我整理</t>
+  </si>
+  <si>
+    <t>年度回顧</t>
+  </si>
+  <si>
+    <t>小旅行</t>
+  </si>
+  <si>
+    <t>河濱路跑</t>
+  </si>
+  <si>
+    <t>團跑</t>
+  </si>
+  <si>
+    <t>咖啡體驗</t>
+  </si>
+  <si>
+    <t>手沖咖啡</t>
+  </si>
+  <si>
+    <t>咖啡對談</t>
+  </si>
+  <si>
+    <t>創傷療癒</t>
+  </si>
+  <si>
+    <t>咖啡辯論</t>
+  </si>
+  <si>
+    <t>深夜對談</t>
+  </si>
+  <si>
+    <t>情緒分享</t>
+  </si>
+  <si>
+    <t>公園聚會</t>
+  </si>
+  <si>
+    <t>運動計畫</t>
+  </si>
+  <si>
+    <t>新年目標</t>
+  </si>
+  <si>
+    <t>公益路跑</t>
+  </si>
+  <si>
+    <t>城市路跑</t>
+  </si>
+  <si>
+    <t>甜點試吃</t>
+  </si>
+  <si>
+    <t>新品發表</t>
+  </si>
+  <si>
+    <t>日出跑</t>
+  </si>
+  <si>
+    <t>早餐團</t>
+  </si>
+  <si>
+    <t>說故事</t>
+  </si>
+  <si>
+    <t>開放舞台</t>
+  </si>
+  <si>
+    <t>深夜跑步</t>
+  </si>
+  <si>
+    <t>情緒釋放</t>
+  </si>
+  <si>
+    <t>閱讀交流</t>
+  </si>
+  <si>
+    <t>自由閱讀</t>
+  </si>
+  <si>
+    <t>插畫展</t>
+  </si>
+  <si>
+    <t>展覽導覽</t>
+  </si>
+  <si>
+    <t>插畫創作</t>
+  </si>
+  <si>
+    <t>情緒主題</t>
+  </si>
+  <si>
+    <t>人體藝術</t>
+  </si>
+  <si>
+    <t>實驗展覽</t>
+  </si>
+  <si>
+    <t>戶外派對</t>
+  </si>
+  <si>
+    <t>美食分享</t>
+  </si>
+  <si>
+    <t>烘焙課</t>
+  </si>
+  <si>
+    <t>甜點實作</t>
+  </si>
+  <si>
+    <t>甜點烘焙</t>
+  </si>
+  <si>
+    <t>失戀療癒</t>
+  </si>
+  <si>
+    <t>假面晚宴</t>
+  </si>
+  <si>
+    <t>社交實驗</t>
+  </si>
+  <si>
+    <t>攝影挑戰</t>
+  </si>
+  <si>
+    <t>攝影散步</t>
+  </si>
+  <si>
+    <t>自由交流</t>
+  </si>
+  <si>
+    <t>聊天聚會</t>
+  </si>
+  <si>
+    <t>戶外露營</t>
+  </si>
+  <si>
+    <t>山林生活</t>
+  </si>
+  <si>
+    <t>山林靜心</t>
+  </si>
+  <si>
+    <t>數位排毒</t>
+  </si>
+  <si>
+    <t>靜默營</t>
+  </si>
+  <si>
+    <t>電子音樂派對</t>
+  </si>
+  <si>
+    <t>技能分享</t>
+  </si>
+  <si>
+    <t>學習交流</t>
+  </si>
+  <si>
+    <t>水彩課</t>
+  </si>
+  <si>
+    <t>基礎繪畫</t>
+  </si>
+  <si>
+    <t>策略競技</t>
+  </si>
+  <si>
+    <t>輕音樂聚會</t>
+  </si>
+  <si>
+    <t>春季派對</t>
+  </si>
+  <si>
+    <t>戶外音樂</t>
+  </si>
+  <si>
+    <t>真實演出</t>
+  </si>
+  <si>
+    <t>實驗音樂</t>
+  </si>
+  <si>
+    <t>音牆體驗</t>
+  </si>
+  <si>
+    <t>咖啡講座</t>
+  </si>
+  <si>
+    <t>風味解析</t>
+  </si>
+  <si>
+    <t>羽球賽</t>
+  </si>
+  <si>
+    <t>競速挑戰</t>
+  </si>
+  <si>
+    <t>自由聚會</t>
+  </si>
+  <si>
+    <t>無主題交流</t>
+  </si>
+  <si>
+    <t>生存策略</t>
+  </si>
+  <si>
+    <t>展覽企劃</t>
+  </si>
+  <si>
+    <t>市集規劃</t>
+  </si>
+  <si>
+    <t>策略對決</t>
+  </si>
+  <si>
+    <t>桌遊對抗</t>
+  </si>
+  <si>
+    <t>解謎活動</t>
+  </si>
+  <si>
+    <t>手作市集</t>
+  </si>
+  <si>
+    <t>品牌展示</t>
+  </si>
+  <si>
+    <t>藝術對談</t>
+  </si>
+  <si>
+    <t>自我探索</t>
+  </si>
+  <si>
+    <t>電影講座</t>
+  </si>
+  <si>
+    <t>煙火旅行</t>
+  </si>
+  <si>
+    <t>跨年活動</t>
+  </si>
+  <si>
+    <t>煙火觀賞</t>
+  </si>
+  <si>
+    <t>跨年沉默</t>
+  </si>
+  <si>
+    <t>煙火倒數</t>
+  </si>
+  <si>
+    <t>年終聚餐</t>
   </si>
 </sst>
 </file>
@@ -275,7 +1184,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -313,6 +1222,13 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -346,7 +1262,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -377,6 +1293,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -659,15 +1578,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H160"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
+  <dimension ref="A1:H482"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="28.625" style="11" customWidth="1"/>
     <col min="3" max="5" width="28.625" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
@@ -678,7 +1597,7 @@
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
@@ -689,12 +1608,12 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:8" s="7" customFormat="1">
+    <row r="3" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="s">
-        <v>4</v>
+      <c r="B3" s="12" t="s">
+        <v>19</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -702,12 +1621,12 @@
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
     </row>
-    <row r="4" spans="1:8" s="7" customFormat="1">
+    <row r="4" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>5</v>
+      <c r="B4" s="12" t="s">
+        <v>20</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -716,12 +1635,12 @@
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
     </row>
-    <row r="5" spans="1:8" s="7" customFormat="1">
+    <row r="5" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10">
         <v>3</v>
       </c>
-      <c r="B5" s="10" t="s">
-        <v>6</v>
+      <c r="B5" s="12" t="s">
+        <v>21</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -730,12 +1649,12 @@
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="10">
         <v>4</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>7</v>
+      <c r="B6" s="12" t="s">
+        <v>22</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -744,22 +1663,22 @@
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="10">
         <v>5</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>8</v>
+      <c r="B7" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="C7" s="2"/>
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="10">
         <v>6</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>9</v>
+      <c r="B8" s="12" t="s">
+        <v>12</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -768,12 +1687,12 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="10">
         <v>7</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>10</v>
+      <c r="B9" s="12" t="s">
+        <v>24</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -782,12 +1701,12 @@
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="10">
         <v>8</v>
       </c>
-      <c r="B10" s="10" t="s">
-        <v>11</v>
+      <c r="B10" s="12" t="s">
+        <v>16</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -796,12 +1715,12 @@
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="10">
         <v>9</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>12</v>
+      <c r="B11" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -810,12 +1729,12 @@
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
         <v>10</v>
       </c>
-      <c r="B12" s="10" t="s">
-        <v>13</v>
+      <c r="B12" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -824,12 +1743,12 @@
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="10">
         <v>11</v>
       </c>
-      <c r="B13" s="10" t="s">
-        <v>14</v>
+      <c r="B13" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -838,12 +1757,12 @@
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="10">
         <v>12</v>
       </c>
-      <c r="B14" s="10" t="s">
-        <v>15</v>
+      <c r="B14" s="12" t="s">
+        <v>28</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -852,12 +1771,12 @@
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="10">
         <v>13</v>
       </c>
-      <c r="B15" s="10" t="s">
-        <v>16</v>
+      <c r="B15" s="12" t="s">
+        <v>29</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -866,12 +1785,12 @@
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="10">
         <v>14</v>
       </c>
-      <c r="B16" s="10" t="s">
-        <v>17</v>
+      <c r="B16" s="12" t="s">
+        <v>30</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -880,12 +1799,12 @@
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="10">
         <v>15</v>
       </c>
-      <c r="B17" s="10" t="s">
-        <v>18</v>
+      <c r="B17" s="12" t="s">
+        <v>31</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -894,12 +1813,12 @@
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
         <v>16</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>19</v>
+      <c r="B18" s="12" t="s">
+        <v>32</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -908,12 +1827,12 @@
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="10">
         <v>17</v>
       </c>
-      <c r="B19" s="10" t="s">
-        <v>20</v>
+      <c r="B19" s="12" t="s">
+        <v>33</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -922,12 +1841,12 @@
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <v>18</v>
       </c>
-      <c r="B20" s="10" t="s">
-        <v>21</v>
+      <c r="B20" s="12" t="s">
+        <v>34</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
@@ -936,12 +1855,12 @@
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="10">
         <v>19</v>
       </c>
-      <c r="B21" s="10" t="s">
-        <v>22</v>
+      <c r="B21" s="12" t="s">
+        <v>35</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
@@ -950,12 +1869,12 @@
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="10">
         <v>20</v>
       </c>
-      <c r="B22" s="10" t="s">
-        <v>23</v>
+      <c r="B22" s="12" t="s">
+        <v>36</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
@@ -964,12 +1883,12 @@
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="10">
         <v>21</v>
       </c>
-      <c r="B23" s="10" t="s">
-        <v>24</v>
+      <c r="B23" s="12" t="s">
+        <v>37</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
@@ -978,12 +1897,12 @@
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
         <v>22</v>
       </c>
-      <c r="B24" s="10" t="s">
-        <v>25</v>
+      <c r="B24" s="12" t="s">
+        <v>38</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
@@ -992,12 +1911,12 @@
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="10">
         <v>23</v>
       </c>
-      <c r="B25" s="10" t="s">
-        <v>26</v>
+      <c r="B25" s="12" t="s">
+        <v>39</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
@@ -1006,12 +1925,12 @@
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>24</v>
       </c>
-      <c r="B26" s="10" t="s">
-        <v>27</v>
+      <c r="B26" s="12" t="s">
+        <v>40</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
@@ -1020,12 +1939,12 @@
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>25</v>
       </c>
-      <c r="B27" s="10" t="s">
-        <v>28</v>
+      <c r="B27" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
@@ -1034,12 +1953,12 @@
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
         <v>26</v>
       </c>
-      <c r="B28" s="10" t="s">
-        <v>29</v>
+      <c r="B28" s="12" t="s">
+        <v>42</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
@@ -1048,12 +1967,12 @@
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>27</v>
       </c>
-      <c r="B29" s="10" t="s">
-        <v>30</v>
+      <c r="B29" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
@@ -1062,12 +1981,12 @@
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>28</v>
       </c>
-      <c r="B30" s="10" t="s">
-        <v>31</v>
+      <c r="B30" s="12" t="s">
+        <v>44</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
@@ -1076,12 +1995,12 @@
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>29</v>
       </c>
-      <c r="B31" s="10" t="s">
-        <v>32</v>
+      <c r="B31" s="12" t="s">
+        <v>45</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
@@ -1090,12 +2009,12 @@
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>30</v>
       </c>
-      <c r="B32" s="10" t="s">
-        <v>33</v>
+      <c r="B32" s="12" t="s">
+        <v>5</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
@@ -1104,12 +2023,12 @@
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>31</v>
       </c>
-      <c r="B33" s="10" t="s">
-        <v>34</v>
+      <c r="B33" s="12" t="s">
+        <v>46</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
@@ -1118,12 +2037,12 @@
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>32</v>
       </c>
-      <c r="B34" s="10" t="s">
-        <v>35</v>
+      <c r="B34" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
@@ -1132,12 +2051,12 @@
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>33</v>
       </c>
-      <c r="B35" s="10" t="s">
-        <v>36</v>
+      <c r="B35" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
@@ -1146,12 +2065,12 @@
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>34</v>
       </c>
-      <c r="B36" s="10" t="s">
-        <v>37</v>
+      <c r="B36" s="12" t="s">
+        <v>49</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
@@ -1160,12 +2079,12 @@
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>35</v>
       </c>
-      <c r="B37" s="10" t="s">
-        <v>38</v>
+      <c r="B37" s="12" t="s">
+        <v>50</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
@@ -1174,12 +2093,12 @@
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>36</v>
       </c>
-      <c r="B38" s="10" t="s">
-        <v>39</v>
+      <c r="B38" s="12" t="s">
+        <v>51</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
@@ -1188,12 +2107,12 @@
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>37</v>
       </c>
-      <c r="B39" s="10" t="s">
-        <v>40</v>
+      <c r="B39" s="12" t="s">
+        <v>52</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
@@ -1202,12 +2121,12 @@
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>38</v>
       </c>
-      <c r="B40" s="10" t="s">
-        <v>41</v>
+      <c r="B40" s="12" t="s">
+        <v>4</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
@@ -1216,12 +2135,12 @@
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>39</v>
       </c>
-      <c r="B41" s="10" t="s">
-        <v>42</v>
+      <c r="B41" s="12" t="s">
+        <v>53</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
@@ -1230,12 +2149,12 @@
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>40</v>
       </c>
-      <c r="B42" s="10" t="s">
-        <v>43</v>
+      <c r="B42" s="12" t="s">
+        <v>54</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
@@ -1244,12 +2163,12 @@
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>41</v>
       </c>
-      <c r="B43" s="10" t="s">
-        <v>44</v>
+      <c r="B43" s="12" t="s">
+        <v>55</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
@@ -1258,12 +2177,12 @@
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>42</v>
       </c>
-      <c r="B44" s="10" t="s">
-        <v>45</v>
+      <c r="B44" s="12" t="s">
+        <v>56</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
@@ -1272,12 +2191,12 @@
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>43</v>
       </c>
-      <c r="B45" s="10" t="s">
-        <v>46</v>
+      <c r="B45" s="12" t="s">
+        <v>57</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
@@ -1286,12 +2205,12 @@
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>44</v>
       </c>
-      <c r="B46" s="10" t="s">
-        <v>47</v>
+      <c r="B46" s="12" t="s">
+        <v>6</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
@@ -1300,12 +2219,12 @@
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>45</v>
       </c>
-      <c r="B47" s="10" t="s">
-        <v>48</v>
+      <c r="B47" s="12" t="s">
+        <v>58</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
@@ -1314,12 +2233,12 @@
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>46</v>
       </c>
-      <c r="B48" s="10" t="s">
-        <v>49</v>
+      <c r="B48" s="12" t="s">
+        <v>59</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
@@ -1328,12 +2247,12 @@
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="10">
         <v>47</v>
       </c>
-      <c r="B49" s="10" t="s">
-        <v>50</v>
+      <c r="B49" s="12" t="s">
+        <v>60</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
@@ -1342,12 +2261,12 @@
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="10">
         <v>48</v>
       </c>
-      <c r="B50" s="10" t="s">
-        <v>51</v>
+      <c r="B50" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
@@ -1356,12 +2275,12 @@
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="10">
         <v>49</v>
       </c>
-      <c r="B51" s="10" t="s">
-        <v>52</v>
+      <c r="B51" s="12" t="s">
+        <v>62</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
@@ -1370,12 +2289,12 @@
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="10">
         <v>50</v>
       </c>
-      <c r="B52" s="10" t="s">
-        <v>53</v>
+      <c r="B52" s="12" t="s">
+        <v>63</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
@@ -1384,12 +2303,12 @@
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="10">
         <v>51</v>
       </c>
-      <c r="B53" s="10" t="s">
-        <v>54</v>
+      <c r="B53" s="12" t="s">
+        <v>64</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
@@ -1398,12 +2317,12 @@
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="10">
         <v>52</v>
       </c>
-      <c r="B54" s="10" t="s">
-        <v>55</v>
+      <c r="B54" s="12" t="s">
+        <v>65</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
@@ -1412,12 +2331,12 @@
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="10">
         <v>53</v>
       </c>
-      <c r="B55" s="10" t="s">
-        <v>56</v>
+      <c r="B55" s="12" t="s">
+        <v>66</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
@@ -1426,12 +2345,12 @@
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="10">
         <v>54</v>
       </c>
-      <c r="B56" s="10" t="s">
-        <v>57</v>
+      <c r="B56" s="12" t="s">
+        <v>67</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
@@ -1440,12 +2359,12 @@
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="10">
         <v>55</v>
       </c>
-      <c r="B57" s="10" t="s">
-        <v>58</v>
+      <c r="B57" s="12" t="s">
+        <v>7</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
@@ -1454,12 +2373,12 @@
       <c r="G57" s="4"/>
       <c r="H57" s="4"/>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="10">
         <v>56</v>
       </c>
-      <c r="B58" s="10" t="s">
-        <v>59</v>
+      <c r="B58" s="12" t="s">
+        <v>8</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" s="2"/>
@@ -1468,12 +2387,12 @@
       <c r="G58" s="4"/>
       <c r="H58" s="4"/>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="10">
         <v>57</v>
       </c>
-      <c r="B59" s="10" t="s">
-        <v>60</v>
+      <c r="B59" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
@@ -1482,12 +2401,12 @@
       <c r="G59" s="4"/>
       <c r="H59" s="4"/>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="10">
         <v>58</v>
       </c>
-      <c r="B60" s="10" t="s">
-        <v>61</v>
+      <c r="B60" s="12" t="s">
+        <v>68</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
@@ -1496,12 +2415,12 @@
       <c r="G60" s="4"/>
       <c r="H60" s="4"/>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="10">
         <v>59</v>
       </c>
-      <c r="B61" s="10" t="s">
-        <v>62</v>
+      <c r="B61" s="12" t="s">
+        <v>69</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
@@ -1510,12 +2429,12 @@
       <c r="G61" s="4"/>
       <c r="H61" s="4"/>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="10">
         <v>60</v>
       </c>
-      <c r="B62" s="10" t="s">
-        <v>63</v>
+      <c r="B62" s="12" t="s">
+        <v>70</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" s="2"/>
@@ -1524,12 +2443,12 @@
       <c r="G62" s="4"/>
       <c r="H62" s="4"/>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="10">
         <v>61</v>
       </c>
-      <c r="B63" s="10" t="s">
-        <v>64</v>
+      <c r="B63" s="12" t="s">
+        <v>71</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
@@ -1538,12 +2457,12 @@
       <c r="G63" s="4"/>
       <c r="H63" s="4"/>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="10">
         <v>62</v>
       </c>
-      <c r="B64" s="10" t="s">
-        <v>65</v>
+      <c r="B64" s="12" t="s">
+        <v>72</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
@@ -1552,12 +2471,12 @@
       <c r="G64" s="4"/>
       <c r="H64" s="4"/>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="10">
         <v>63</v>
       </c>
-      <c r="B65" s="10" t="s">
-        <v>66</v>
+      <c r="B65" s="12" t="s">
+        <v>73</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
@@ -1566,12 +2485,12 @@
       <c r="G65" s="4"/>
       <c r="H65" s="4"/>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="10">
         <v>64</v>
       </c>
-      <c r="B66" s="10" t="s">
-        <v>67</v>
+      <c r="B66" s="12" t="s">
+        <v>74</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" s="2"/>
@@ -1580,12 +2499,12 @@
       <c r="G66" s="4"/>
       <c r="H66" s="4"/>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="10">
         <v>65</v>
       </c>
-      <c r="B67" s="10" t="s">
-        <v>68</v>
+      <c r="B67" s="12" t="s">
+        <v>75</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" s="2"/>
@@ -1594,12 +2513,12 @@
       <c r="G67" s="4"/>
       <c r="H67" s="4"/>
     </row>
-    <row r="68" spans="1:8">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="10">
         <v>66</v>
       </c>
-      <c r="B68" s="10" t="s">
-        <v>69</v>
+      <c r="B68" s="12" t="s">
+        <v>76</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" s="2"/>
@@ -1608,12 +2527,12 @@
       <c r="G68" s="4"/>
       <c r="H68" s="4"/>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="10">
         <v>67</v>
       </c>
-      <c r="B69" s="10" t="s">
-        <v>70</v>
+      <c r="B69" s="12" t="s">
+        <v>77</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
@@ -1622,12 +2541,12 @@
       <c r="G69" s="4"/>
       <c r="H69" s="4"/>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="10">
         <v>68</v>
       </c>
-      <c r="B70" s="10" t="s">
-        <v>71</v>
+      <c r="B70" s="12" t="s">
+        <v>78</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" s="2"/>
@@ -1636,12 +2555,12 @@
       <c r="G70" s="4"/>
       <c r="H70" s="4"/>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="10">
         <v>69</v>
       </c>
-      <c r="B71" s="10" t="s">
-        <v>72</v>
+      <c r="B71" s="12" t="s">
+        <v>79</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" s="2"/>
@@ -1650,12 +2569,12 @@
       <c r="G71" s="4"/>
       <c r="H71" s="4"/>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="10">
         <v>70</v>
       </c>
-      <c r="B72" s="10" t="s">
-        <v>73</v>
+      <c r="B72" s="12" t="s">
+        <v>80</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" s="2"/>
@@ -1664,12 +2583,12 @@
       <c r="G72" s="4"/>
       <c r="H72" s="4"/>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="10">
         <v>71</v>
       </c>
-      <c r="B73" s="10" t="s">
-        <v>74</v>
+      <c r="B73" s="12" t="s">
+        <v>81</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" s="2"/>
@@ -1678,12 +2597,12 @@
       <c r="G73" s="4"/>
       <c r="H73" s="4"/>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="10">
         <v>72</v>
       </c>
-      <c r="B74" s="10" t="s">
-        <v>75</v>
+      <c r="B74" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" s="2"/>
@@ -1692,12 +2611,12 @@
       <c r="G74" s="4"/>
       <c r="H74" s="4"/>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="10">
         <v>73</v>
       </c>
-      <c r="B75" s="10" t="s">
-        <v>76</v>
+      <c r="B75" s="12" t="s">
+        <v>83</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" s="2"/>
@@ -1706,12 +2625,12 @@
       <c r="G75" s="4"/>
       <c r="H75" s="4"/>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="10">
         <v>74</v>
       </c>
-      <c r="B76" s="10" t="s">
-        <v>77</v>
+      <c r="B76" s="12" t="s">
+        <v>84</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" s="2"/>
@@ -1720,12 +2639,12 @@
       <c r="G76" s="4"/>
       <c r="H76" s="4"/>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="10">
         <v>75</v>
       </c>
-      <c r="B77" s="10" t="s">
-        <v>78</v>
+      <c r="B77" s="12" t="s">
+        <v>85</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" s="2"/>
@@ -1734,9 +2653,13 @@
       <c r="G77" s="4"/>
       <c r="H77" s="4"/>
     </row>
-    <row r="78" spans="1:8">
-      <c r="A78" s="10"/>
-      <c r="B78" s="10"/>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A78" s="10">
+        <v>76</v>
+      </c>
+      <c r="B78" s="12" t="s">
+        <v>86</v>
+      </c>
       <c r="C78" s="2"/>
       <c r="D78" s="2"/>
       <c r="E78" s="2"/>
@@ -1744,9 +2667,13 @@
       <c r="G78" s="4"/>
       <c r="H78" s="4"/>
     </row>
-    <row r="79" spans="1:8">
-      <c r="A79" s="10"/>
-      <c r="B79" s="10"/>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A79" s="10">
+        <v>77</v>
+      </c>
+      <c r="B79" s="12" t="s">
+        <v>87</v>
+      </c>
       <c r="C79" s="2"/>
       <c r="D79" s="2"/>
       <c r="E79" s="2"/>
@@ -1754,9 +2681,13 @@
       <c r="G79" s="4"/>
       <c r="H79" s="4"/>
     </row>
-    <row r="80" spans="1:8">
-      <c r="A80" s="10"/>
-      <c r="B80" s="10"/>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A80" s="10">
+        <v>78</v>
+      </c>
+      <c r="B80" s="12" t="s">
+        <v>88</v>
+      </c>
       <c r="C80" s="2"/>
       <c r="D80" s="2"/>
       <c r="E80" s="2"/>
@@ -1764,9 +2695,13 @@
       <c r="G80" s="4"/>
       <c r="H80" s="4"/>
     </row>
-    <row r="81" spans="1:8">
-      <c r="A81" s="10"/>
-      <c r="B81" s="10"/>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A81" s="10">
+        <v>79</v>
+      </c>
+      <c r="B81" s="12" t="s">
+        <v>89</v>
+      </c>
       <c r="C81" s="2"/>
       <c r="D81" s="2"/>
       <c r="E81" s="2"/>
@@ -1774,9 +2709,13 @@
       <c r="G81" s="4"/>
       <c r="H81" s="4"/>
     </row>
-    <row r="82" spans="1:8">
-      <c r="A82" s="10"/>
-      <c r="B82" s="10"/>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A82" s="10">
+        <v>80</v>
+      </c>
+      <c r="B82" s="12" t="s">
+        <v>90</v>
+      </c>
       <c r="C82" s="2"/>
       <c r="D82" s="2"/>
       <c r="E82" s="2"/>
@@ -1784,9 +2723,13 @@
       <c r="G82" s="4"/>
       <c r="H82" s="4"/>
     </row>
-    <row r="83" spans="1:8">
-      <c r="A83" s="10"/>
-      <c r="B83" s="10"/>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A83" s="10">
+        <v>81</v>
+      </c>
+      <c r="B83" s="12" t="s">
+        <v>91</v>
+      </c>
       <c r="C83" s="2"/>
       <c r="D83" s="2"/>
       <c r="E83" s="2"/>
@@ -1794,9 +2737,13 @@
       <c r="G83" s="4"/>
       <c r="H83" s="4"/>
     </row>
-    <row r="84" spans="1:8">
-      <c r="A84" s="10"/>
-      <c r="B84" s="10"/>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A84" s="10">
+        <v>82</v>
+      </c>
+      <c r="B84" s="12" t="s">
+        <v>92</v>
+      </c>
       <c r="C84" s="2"/>
       <c r="D84" s="2"/>
       <c r="E84" s="2"/>
@@ -1804,9 +2751,13 @@
       <c r="G84" s="4"/>
       <c r="H84" s="4"/>
     </row>
-    <row r="85" spans="1:8">
-      <c r="A85" s="10"/>
-      <c r="B85" s="10"/>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A85" s="10">
+        <v>83</v>
+      </c>
+      <c r="B85" s="12" t="s">
+        <v>93</v>
+      </c>
       <c r="C85" s="2"/>
       <c r="D85" s="2"/>
       <c r="E85" s="2"/>
@@ -1814,9 +2765,13 @@
       <c r="G85" s="4"/>
       <c r="H85" s="4"/>
     </row>
-    <row r="86" spans="1:8">
-      <c r="A86" s="10"/>
-      <c r="B86" s="10"/>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A86" s="10">
+        <v>84</v>
+      </c>
+      <c r="B86" s="12" t="s">
+        <v>94</v>
+      </c>
       <c r="C86" s="2"/>
       <c r="D86" s="2"/>
       <c r="E86" s="2"/>
@@ -1824,9 +2779,13 @@
       <c r="G86" s="4"/>
       <c r="H86" s="4"/>
     </row>
-    <row r="87" spans="1:8">
-      <c r="A87" s="10"/>
-      <c r="B87" s="10"/>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A87" s="10">
+        <v>85</v>
+      </c>
+      <c r="B87" s="12" t="s">
+        <v>95</v>
+      </c>
       <c r="C87" s="2"/>
       <c r="D87" s="2"/>
       <c r="E87" s="2"/>
@@ -1834,9 +2793,13 @@
       <c r="G87" s="4"/>
       <c r="H87" s="4"/>
     </row>
-    <row r="88" spans="1:8">
-      <c r="A88" s="10"/>
-      <c r="B88" s="10"/>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A88" s="10">
+        <v>86</v>
+      </c>
+      <c r="B88" s="12" t="s">
+        <v>96</v>
+      </c>
       <c r="C88" s="2"/>
       <c r="D88" s="2"/>
       <c r="E88" s="2"/>
@@ -1844,9 +2807,13 @@
       <c r="G88" s="4"/>
       <c r="H88" s="4"/>
     </row>
-    <row r="89" spans="1:8">
-      <c r="A89" s="10"/>
-      <c r="B89" s="10"/>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A89" s="10">
+        <v>87</v>
+      </c>
+      <c r="B89" s="12" t="s">
+        <v>97</v>
+      </c>
       <c r="C89" s="2"/>
       <c r="D89" s="2"/>
       <c r="E89" s="2"/>
@@ -1854,9 +2821,13 @@
       <c r="G89" s="4"/>
       <c r="H89" s="4"/>
     </row>
-    <row r="90" spans="1:8">
-      <c r="A90" s="10"/>
-      <c r="B90" s="10"/>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A90" s="10">
+        <v>88</v>
+      </c>
+      <c r="B90" s="12" t="s">
+        <v>10</v>
+      </c>
       <c r="C90" s="2"/>
       <c r="D90" s="2"/>
       <c r="E90" s="2"/>
@@ -1864,9 +2835,13 @@
       <c r="G90" s="4"/>
       <c r="H90" s="4"/>
     </row>
-    <row r="91" spans="1:8">
-      <c r="A91" s="10"/>
-      <c r="B91" s="10"/>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A91" s="10">
+        <v>89</v>
+      </c>
+      <c r="B91" s="12" t="s">
+        <v>98</v>
+      </c>
       <c r="C91" s="2"/>
       <c r="D91" s="2"/>
       <c r="E91" s="2"/>
@@ -1874,9 +2849,13 @@
       <c r="G91" s="4"/>
       <c r="H91" s="4"/>
     </row>
-    <row r="92" spans="1:8">
-      <c r="A92" s="10"/>
-      <c r="B92" s="10"/>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A92" s="10">
+        <v>90</v>
+      </c>
+      <c r="B92" s="12" t="s">
+        <v>15</v>
+      </c>
       <c r="C92" s="2"/>
       <c r="D92" s="2"/>
       <c r="E92" s="2"/>
@@ -1884,9 +2863,13 @@
       <c r="G92" s="4"/>
       <c r="H92" s="4"/>
     </row>
-    <row r="93" spans="1:8">
-      <c r="A93" s="10"/>
-      <c r="B93" s="10"/>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A93" s="10">
+        <v>91</v>
+      </c>
+      <c r="B93" s="12" t="s">
+        <v>99</v>
+      </c>
       <c r="C93" s="2"/>
       <c r="D93" s="2"/>
       <c r="E93" s="2"/>
@@ -1894,9 +2877,13 @@
       <c r="G93" s="4"/>
       <c r="H93" s="4"/>
     </row>
-    <row r="94" spans="1:8">
-      <c r="A94" s="10"/>
-      <c r="B94" s="10"/>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A94" s="10">
+        <v>92</v>
+      </c>
+      <c r="B94" s="12" t="s">
+        <v>100</v>
+      </c>
       <c r="C94" s="2"/>
       <c r="D94" s="2"/>
       <c r="E94" s="2"/>
@@ -1904,9 +2891,13 @@
       <c r="G94" s="4"/>
       <c r="H94" s="4"/>
     </row>
-    <row r="95" spans="1:8">
-      <c r="A95" s="10"/>
-      <c r="B95" s="10"/>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A95" s="10">
+        <v>93</v>
+      </c>
+      <c r="B95" s="12" t="s">
+        <v>101</v>
+      </c>
       <c r="C95" s="2"/>
       <c r="D95" s="2"/>
       <c r="E95" s="2"/>
@@ -1914,9 +2905,13 @@
       <c r="G95" s="4"/>
       <c r="H95" s="4"/>
     </row>
-    <row r="96" spans="1:8">
-      <c r="A96" s="10"/>
-      <c r="B96" s="10"/>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A96" s="10">
+        <v>94</v>
+      </c>
+      <c r="B96" s="12" t="s">
+        <v>11</v>
+      </c>
       <c r="C96" s="2"/>
       <c r="D96" s="2"/>
       <c r="E96" s="2"/>
@@ -1924,9 +2919,13 @@
       <c r="G96" s="4"/>
       <c r="H96" s="4"/>
     </row>
-    <row r="97" spans="1:8">
-      <c r="A97" s="10"/>
-      <c r="B97" s="10"/>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A97" s="10">
+        <v>95</v>
+      </c>
+      <c r="B97" s="12" t="s">
+        <v>102</v>
+      </c>
       <c r="C97" s="2"/>
       <c r="D97" s="2"/>
       <c r="E97" s="2"/>
@@ -1934,9 +2933,13 @@
       <c r="G97" s="4"/>
       <c r="H97" s="4"/>
     </row>
-    <row r="98" spans="1:8">
-      <c r="A98" s="10"/>
-      <c r="B98" s="10"/>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A98" s="10">
+        <v>96</v>
+      </c>
+      <c r="B98" s="12" t="s">
+        <v>103</v>
+      </c>
       <c r="C98" s="2"/>
       <c r="D98" s="2"/>
       <c r="E98" s="2"/>
@@ -1944,364 +2947,2728 @@
       <c r="G98" s="4"/>
       <c r="H98" s="4"/>
     </row>
-    <row r="99" spans="1:8">
-      <c r="A99" s="10"/>
-      <c r="B99" s="10"/>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A99" s="10">
+        <v>97</v>
+      </c>
+      <c r="B99" s="12" t="s">
+        <v>104</v>
+      </c>
       <c r="C99" s="2"/>
       <c r="D99" s="2"/>
       <c r="E99" s="2"/>
     </row>
-    <row r="100" spans="1:8">
-      <c r="A100" s="10"/>
-      <c r="B100" s="10"/>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A100" s="10">
+        <v>98</v>
+      </c>
+      <c r="B100" s="12" t="s">
+        <v>105</v>
+      </c>
       <c r="C100" s="2"/>
       <c r="D100" s="2"/>
       <c r="E100" s="2"/>
     </row>
-    <row r="101" spans="1:8">
-      <c r="A101" s="10"/>
-      <c r="B101" s="10"/>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A101" s="10">
+        <v>99</v>
+      </c>
+      <c r="B101" s="12" t="s">
+        <v>106</v>
+      </c>
       <c r="C101" s="2"/>
       <c r="D101" s="2"/>
       <c r="E101" s="2"/>
     </row>
-    <row r="102" spans="1:8">
-      <c r="A102" s="10"/>
-      <c r="B102" s="10"/>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A102" s="10">
+        <v>100</v>
+      </c>
+      <c r="B102" s="12" t="s">
+        <v>107</v>
+      </c>
       <c r="C102" s="2"/>
       <c r="D102" s="2"/>
       <c r="E102" s="2"/>
     </row>
-    <row r="103" spans="1:8">
-      <c r="A103" s="10"/>
-      <c r="B103" s="10"/>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A103" s="10">
+        <v>101</v>
+      </c>
+      <c r="B103" s="12" t="s">
+        <v>108</v>
+      </c>
       <c r="C103" s="2"/>
       <c r="D103" s="2"/>
       <c r="E103" s="2"/>
     </row>
-    <row r="104" spans="1:8">
-      <c r="A104" s="10"/>
-      <c r="B104" s="10"/>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A104" s="10">
+        <v>102</v>
+      </c>
+      <c r="B104" s="12" t="s">
+        <v>109</v>
+      </c>
       <c r="C104" s="2"/>
       <c r="D104" s="2"/>
       <c r="E104" s="2"/>
     </row>
-    <row r="105" spans="1:8">
-      <c r="A105" s="10"/>
-      <c r="B105" s="10"/>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A105" s="10">
+        <v>103</v>
+      </c>
+      <c r="B105" s="12" t="s">
+        <v>110</v>
+      </c>
       <c r="C105" s="2"/>
       <c r="D105" s="2"/>
       <c r="E105" s="2"/>
     </row>
-    <row r="106" spans="1:8">
-      <c r="A106" s="10"/>
-      <c r="B106" s="10"/>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A106" s="10">
+        <v>104</v>
+      </c>
+      <c r="B106" s="12" t="s">
+        <v>111</v>
+      </c>
       <c r="C106" s="2"/>
       <c r="D106" s="2"/>
       <c r="E106" s="2"/>
     </row>
-    <row r="107" spans="1:8">
-      <c r="A107" s="10"/>
-      <c r="B107" s="10"/>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A107" s="10">
+        <v>105</v>
+      </c>
+      <c r="B107" s="12" t="s">
+        <v>112</v>
+      </c>
       <c r="C107" s="2"/>
       <c r="D107" s="2"/>
       <c r="E107" s="2"/>
     </row>
-    <row r="108" spans="1:8">
-      <c r="A108" s="10"/>
-      <c r="B108" s="10"/>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A108" s="10">
+        <v>106</v>
+      </c>
+      <c r="B108" s="12" t="s">
+        <v>113</v>
+      </c>
       <c r="C108" s="2"/>
       <c r="D108" s="2"/>
       <c r="E108" s="2"/>
     </row>
-    <row r="109" spans="1:8">
-      <c r="A109" s="10"/>
-      <c r="B109" s="10"/>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A109" s="10">
+        <v>107</v>
+      </c>
+      <c r="B109" s="12" t="s">
+        <v>114</v>
+      </c>
       <c r="C109" s="2"/>
       <c r="D109" s="2"/>
       <c r="E109" s="2"/>
     </row>
-    <row r="110" spans="1:8">
-      <c r="A110" s="10"/>
-      <c r="B110" s="10"/>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A110" s="10">
+        <v>108</v>
+      </c>
+      <c r="B110" s="12" t="s">
+        <v>115</v>
+      </c>
       <c r="C110" s="2"/>
       <c r="D110" s="2"/>
       <c r="E110" s="2"/>
     </row>
-    <row r="111" spans="1:8">
-      <c r="A111" s="10"/>
-      <c r="B111" s="10"/>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A111" s="10">
+        <v>109</v>
+      </c>
+      <c r="B111" s="12" t="s">
+        <v>116</v>
+      </c>
       <c r="C111" s="2"/>
       <c r="D111" s="2"/>
       <c r="E111" s="2"/>
     </row>
-    <row r="112" spans="1:8">
-      <c r="A112" s="10"/>
-      <c r="B112" s="10"/>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A112" s="10">
+        <v>110</v>
+      </c>
+      <c r="B112" s="12" t="s">
+        <v>117</v>
+      </c>
       <c r="C112" s="2"/>
       <c r="D112" s="2"/>
       <c r="E112" s="2"/>
     </row>
-    <row r="113" spans="1:5">
-      <c r="A113" s="10"/>
-      <c r="B113" s="10"/>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A113" s="10">
+        <v>111</v>
+      </c>
+      <c r="B113" s="12" t="s">
+        <v>118</v>
+      </c>
       <c r="C113" s="2"/>
       <c r="D113" s="2"/>
       <c r="E113" s="2"/>
     </row>
-    <row r="114" spans="1:5">
-      <c r="A114" s="10"/>
-      <c r="B114" s="10"/>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A114" s="10">
+        <v>112</v>
+      </c>
+      <c r="B114" s="12" t="s">
+        <v>119</v>
+      </c>
       <c r="C114" s="2"/>
       <c r="D114" s="2"/>
       <c r="E114" s="2"/>
     </row>
-    <row r="115" spans="1:5">
-      <c r="A115" s="10"/>
-      <c r="B115" s="10"/>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A115" s="10">
+        <v>113</v>
+      </c>
+      <c r="B115" s="12" t="s">
+        <v>120</v>
+      </c>
       <c r="C115" s="2"/>
       <c r="D115" s="2"/>
       <c r="E115" s="2"/>
     </row>
-    <row r="116" spans="1:5">
-      <c r="A116" s="10"/>
-      <c r="B116" s="10"/>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A116" s="10">
+        <v>114</v>
+      </c>
+      <c r="B116" s="12" t="s">
+        <v>121</v>
+      </c>
       <c r="C116" s="2"/>
       <c r="D116" s="2"/>
       <c r="E116" s="2"/>
     </row>
-    <row r="117" spans="1:5">
-      <c r="A117" s="10"/>
-      <c r="B117" s="10"/>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A117" s="10">
+        <v>115</v>
+      </c>
+      <c r="B117" s="12" t="s">
+        <v>122</v>
+      </c>
       <c r="C117" s="2"/>
       <c r="D117" s="2"/>
       <c r="E117" s="2"/>
     </row>
-    <row r="118" spans="1:5">
-      <c r="A118" s="10"/>
-      <c r="B118" s="10"/>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A118" s="10">
+        <v>116</v>
+      </c>
+      <c r="B118" s="12" t="s">
+        <v>123</v>
+      </c>
       <c r="C118" s="2"/>
       <c r="D118" s="2"/>
       <c r="E118" s="2"/>
     </row>
-    <row r="119" spans="1:5">
-      <c r="A119" s="10"/>
-      <c r="B119" s="10"/>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A119" s="10">
+        <v>117</v>
+      </c>
+      <c r="B119" s="12" t="s">
+        <v>124</v>
+      </c>
       <c r="C119" s="2"/>
       <c r="D119" s="2"/>
       <c r="E119" s="2"/>
     </row>
-    <row r="120" spans="1:5">
-      <c r="A120" s="10"/>
-      <c r="B120" s="10"/>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A120" s="10">
+        <v>118</v>
+      </c>
+      <c r="B120" s="12" t="s">
+        <v>125</v>
+      </c>
       <c r="C120" s="2"/>
       <c r="D120" s="2"/>
       <c r="E120" s="2"/>
     </row>
-    <row r="121" spans="1:5">
-      <c r="A121" s="10"/>
-      <c r="B121" s="10"/>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A121" s="10">
+        <v>119</v>
+      </c>
+      <c r="B121" s="12" t="s">
+        <v>126</v>
+      </c>
       <c r="C121" s="2"/>
       <c r="D121" s="2"/>
       <c r="E121" s="2"/>
     </row>
-    <row r="122" spans="1:5">
-      <c r="A122" s="10"/>
-      <c r="B122" s="10"/>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A122" s="10">
+        <v>120</v>
+      </c>
+      <c r="B122" s="12" t="s">
+        <v>127</v>
+      </c>
       <c r="C122" s="2"/>
       <c r="D122" s="2"/>
       <c r="E122" s="2"/>
     </row>
-    <row r="123" spans="1:5">
-      <c r="A123" s="10"/>
-      <c r="B123" s="10"/>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A123" s="10">
+        <v>121</v>
+      </c>
+      <c r="B123" s="12" t="s">
+        <v>128</v>
+      </c>
       <c r="C123" s="2"/>
       <c r="D123" s="2"/>
       <c r="E123" s="2"/>
     </row>
-    <row r="124" spans="1:5">
-      <c r="A124" s="10"/>
-      <c r="B124" s="10"/>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A124" s="10">
+        <v>122</v>
+      </c>
+      <c r="B124" s="12" t="s">
+        <v>129</v>
+      </c>
       <c r="C124" s="2"/>
       <c r="D124" s="2"/>
       <c r="E124" s="2"/>
     </row>
-    <row r="125" spans="1:5">
-      <c r="A125" s="10"/>
-      <c r="B125" s="10"/>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A125" s="10">
+        <v>123</v>
+      </c>
+      <c r="B125" s="12" t="s">
+        <v>130</v>
+      </c>
       <c r="C125" s="2"/>
       <c r="D125" s="2"/>
       <c r="E125" s="2"/>
     </row>
-    <row r="126" spans="1:5">
-      <c r="A126" s="10"/>
-      <c r="B126" s="10"/>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A126" s="10">
+        <v>124</v>
+      </c>
+      <c r="B126" s="12" t="s">
+        <v>131</v>
+      </c>
       <c r="C126" s="2"/>
       <c r="D126" s="2"/>
       <c r="E126" s="2"/>
     </row>
-    <row r="127" spans="1:5">
-      <c r="A127" s="10"/>
-      <c r="B127" s="10"/>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A127" s="10">
+        <v>125</v>
+      </c>
+      <c r="B127" s="12" t="s">
+        <v>132</v>
+      </c>
       <c r="C127" s="2"/>
       <c r="D127" s="2"/>
       <c r="E127" s="2"/>
     </row>
-    <row r="128" spans="1:5">
-      <c r="A128" s="10"/>
-      <c r="B128" s="10"/>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A128" s="10">
+        <v>126</v>
+      </c>
+      <c r="B128" s="12" t="s">
+        <v>133</v>
+      </c>
       <c r="C128" s="2"/>
       <c r="D128" s="2"/>
       <c r="E128" s="2"/>
     </row>
-    <row r="129" spans="1:5">
-      <c r="A129" s="10"/>
-      <c r="B129" s="10"/>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A129" s="10">
+        <v>127</v>
+      </c>
+      <c r="B129" s="12" t="s">
+        <v>134</v>
+      </c>
       <c r="C129" s="2"/>
       <c r="D129" s="2"/>
       <c r="E129" s="2"/>
     </row>
-    <row r="130" spans="1:5">
-      <c r="A130" s="10"/>
-      <c r="B130" s="10"/>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A130" s="10">
+        <v>128</v>
+      </c>
+      <c r="B130" s="12" t="s">
+        <v>135</v>
+      </c>
       <c r="C130" s="2"/>
       <c r="D130" s="2"/>
       <c r="E130" s="2"/>
     </row>
-    <row r="131" spans="1:5">
-      <c r="A131" s="10"/>
-      <c r="B131" s="10"/>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A131" s="10">
+        <v>129</v>
+      </c>
+      <c r="B131" s="12" t="s">
+        <v>136</v>
+      </c>
       <c r="C131" s="2"/>
       <c r="D131" s="2"/>
       <c r="E131" s="2"/>
     </row>
-    <row r="132" spans="1:5">
-      <c r="A132" s="10"/>
-      <c r="B132" s="10"/>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A132" s="10">
+        <v>130</v>
+      </c>
+      <c r="B132" s="12" t="s">
+        <v>137</v>
+      </c>
       <c r="C132" s="2"/>
       <c r="D132" s="2"/>
       <c r="E132" s="2"/>
     </row>
-    <row r="133" spans="1:5">
-      <c r="A133" s="10"/>
-      <c r="B133" s="10"/>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A133" s="10">
+        <v>131</v>
+      </c>
+      <c r="B133" s="12" t="s">
+        <v>138</v>
+      </c>
       <c r="C133" s="2"/>
       <c r="D133" s="2"/>
       <c r="E133" s="2"/>
     </row>
-    <row r="134" spans="1:5">
-      <c r="A134" s="10"/>
-      <c r="B134" s="10"/>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A134" s="10">
+        <v>132</v>
+      </c>
+      <c r="B134" s="12" t="s">
+        <v>139</v>
+      </c>
       <c r="C134" s="2"/>
       <c r="D134" s="2"/>
       <c r="E134" s="2"/>
     </row>
-    <row r="135" spans="1:5">
-      <c r="A135" s="10"/>
-      <c r="B135" s="10"/>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A135" s="10">
+        <v>133</v>
+      </c>
+      <c r="B135" s="12" t="s">
+        <v>140</v>
+      </c>
       <c r="C135" s="2"/>
       <c r="D135" s="2"/>
       <c r="E135" s="2"/>
     </row>
-    <row r="136" spans="1:5">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A136" s="10">
+        <v>134</v>
+      </c>
+      <c r="B136" s="12" t="s">
+        <v>141</v>
+      </c>
       <c r="C136" s="5"/>
       <c r="D136" s="5"/>
     </row>
-    <row r="137" spans="1:5">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A137" s="10">
+        <v>135</v>
+      </c>
+      <c r="B137" s="12" t="s">
+        <v>142</v>
+      </c>
       <c r="C137" s="5"/>
       <c r="D137" s="5"/>
     </row>
-    <row r="138" spans="1:5">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A138" s="10">
+        <v>136</v>
+      </c>
+      <c r="B138" s="12" t="s">
+        <v>143</v>
+      </c>
       <c r="C138" s="5"/>
       <c r="D138" s="5"/>
     </row>
-    <row r="139" spans="1:5">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A139" s="10">
+        <v>137</v>
+      </c>
+      <c r="B139" s="12" t="s">
+        <v>144</v>
+      </c>
       <c r="C139" s="5"/>
       <c r="D139" s="5"/>
     </row>
-    <row r="140" spans="1:5">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A140" s="10">
+        <v>138</v>
+      </c>
+      <c r="B140" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="C140" s="5"/>
       <c r="D140" s="5"/>
     </row>
-    <row r="141" spans="1:5">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A141" s="10">
+        <v>139</v>
+      </c>
+      <c r="B141" s="12" t="s">
+        <v>146</v>
+      </c>
       <c r="C141" s="5"/>
       <c r="D141" s="5"/>
     </row>
-    <row r="142" spans="1:5">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A142" s="10">
+        <v>140</v>
+      </c>
+      <c r="B142" s="12" t="s">
+        <v>147</v>
+      </c>
       <c r="C142" s="5"/>
       <c r="D142" s="5"/>
     </row>
-    <row r="143" spans="1:5">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A143" s="10">
+        <v>141</v>
+      </c>
+      <c r="B143" s="12" t="s">
+        <v>148</v>
+      </c>
       <c r="C143" s="5"/>
       <c r="D143" s="5"/>
     </row>
-    <row r="144" spans="1:5">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A144" s="10">
+        <v>142</v>
+      </c>
+      <c r="B144" s="12" t="s">
+        <v>149</v>
+      </c>
       <c r="C144" s="5"/>
       <c r="D144" s="5"/>
     </row>
-    <row r="145" spans="3:4">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A145" s="10">
+        <v>143</v>
+      </c>
+      <c r="B145" s="12" t="s">
+        <v>150</v>
+      </c>
       <c r="C145" s="5"/>
       <c r="D145" s="5"/>
     </row>
-    <row r="146" spans="3:4">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A146" s="10">
+        <v>144</v>
+      </c>
+      <c r="B146" s="12" t="s">
+        <v>151</v>
+      </c>
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
     </row>
-    <row r="147" spans="3:4">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A147" s="10">
+        <v>145</v>
+      </c>
+      <c r="B147" s="12" t="s">
+        <v>152</v>
+      </c>
       <c r="C147" s="3"/>
       <c r="D147" s="3"/>
     </row>
-    <row r="148" spans="3:4">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A148" s="10">
+        <v>146</v>
+      </c>
+      <c r="B148" s="12" t="s">
+        <v>153</v>
+      </c>
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
     </row>
-    <row r="149" spans="3:4">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A149" s="10">
+        <v>147</v>
+      </c>
+      <c r="B149" s="12" t="s">
+        <v>13</v>
+      </c>
       <c r="C149" s="3"/>
       <c r="D149" s="3"/>
     </row>
-    <row r="150" spans="3:4">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A150" s="10">
+        <v>148</v>
+      </c>
+      <c r="B150" s="12" t="s">
+        <v>154</v>
+      </c>
       <c r="C150" s="3"/>
       <c r="D150" s="3"/>
     </row>
-    <row r="151" spans="3:4">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A151" s="10">
+        <v>149</v>
+      </c>
+      <c r="B151" s="12" t="s">
+        <v>155</v>
+      </c>
       <c r="C151" s="3"/>
       <c r="D151" s="3"/>
     </row>
-    <row r="152" spans="3:4">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A152" s="10">
+        <v>150</v>
+      </c>
+      <c r="B152" s="12" t="s">
+        <v>156</v>
+      </c>
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
     </row>
-    <row r="153" spans="3:4">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A153" s="10">
+        <v>151</v>
+      </c>
+      <c r="B153" s="12" t="s">
+        <v>157</v>
+      </c>
       <c r="C153" s="3"/>
       <c r="D153" s="3"/>
     </row>
-    <row r="154" spans="3:4">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A154" s="10">
+        <v>152</v>
+      </c>
+      <c r="B154" s="12" t="s">
+        <v>158</v>
+      </c>
       <c r="C154" s="3"/>
       <c r="D154" s="3"/>
     </row>
-    <row r="155" spans="3:4">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A155" s="10">
+        <v>153</v>
+      </c>
+      <c r="B155" s="12" t="s">
+        <v>159</v>
+      </c>
       <c r="C155" s="3"/>
       <c r="D155" s="3"/>
     </row>
-    <row r="156" spans="3:4">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A156" s="10">
+        <v>154</v>
+      </c>
+      <c r="B156" s="12" t="s">
+        <v>160</v>
+      </c>
       <c r="C156" s="3"/>
       <c r="D156" s="3"/>
     </row>
-    <row r="157" spans="3:4">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A157" s="10">
+        <v>155</v>
+      </c>
+      <c r="B157" s="12" t="s">
+        <v>161</v>
+      </c>
       <c r="C157" s="3"/>
       <c r="D157" s="3"/>
     </row>
-    <row r="158" spans="3:4">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A158" s="10">
+        <v>156</v>
+      </c>
+      <c r="B158" s="12" t="s">
+        <v>162</v>
+      </c>
       <c r="C158" s="3"/>
       <c r="D158" s="3"/>
     </row>
-    <row r="159" spans="3:4">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A159" s="10">
+        <v>157</v>
+      </c>
+      <c r="B159" s="12" t="s">
+        <v>163</v>
+      </c>
       <c r="C159" s="3"/>
       <c r="D159" s="3"/>
     </row>
-    <row r="160" spans="3:4">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A160" s="10">
+        <v>158</v>
+      </c>
+      <c r="B160" s="12" t="s">
+        <v>164</v>
+      </c>
       <c r="C160" s="3"/>
       <c r="D160" s="3"/>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A161" s="10">
+        <v>159</v>
+      </c>
+      <c r="B161" s="12" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A162" s="10">
+        <v>160</v>
+      </c>
+      <c r="B162" s="12" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A163" s="10">
+        <v>161</v>
+      </c>
+      <c r="B163" s="12" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A164" s="10">
+        <v>162</v>
+      </c>
+      <c r="B164" s="12" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A165" s="10">
+        <v>163</v>
+      </c>
+      <c r="B165" s="12" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A166" s="10">
+        <v>164</v>
+      </c>
+      <c r="B166" s="12" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A167" s="10">
+        <v>165</v>
+      </c>
+      <c r="B167" s="12" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A168" s="10">
+        <v>166</v>
+      </c>
+      <c r="B168" s="12" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A169" s="10">
+        <v>167</v>
+      </c>
+      <c r="B169" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A170" s="10">
+        <v>168</v>
+      </c>
+      <c r="B170" s="12" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A171" s="10">
+        <v>169</v>
+      </c>
+      <c r="B171" s="12" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A172" s="10">
+        <v>170</v>
+      </c>
+      <c r="B172" s="12" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A173" s="10">
+        <v>171</v>
+      </c>
+      <c r="B173" s="12" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A174" s="10">
+        <v>172</v>
+      </c>
+      <c r="B174" s="12" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A175" s="10">
+        <v>173</v>
+      </c>
+      <c r="B175" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A176" s="10">
+        <v>174</v>
+      </c>
+      <c r="B176" s="12" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A177" s="10">
+        <v>175</v>
+      </c>
+      <c r="B177" s="12" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A178" s="10">
+        <v>176</v>
+      </c>
+      <c r="B178" s="12" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A179" s="10">
+        <v>177</v>
+      </c>
+      <c r="B179" s="12" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A180" s="10">
+        <v>178</v>
+      </c>
+      <c r="B180" s="12" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A181" s="10">
+        <v>179</v>
+      </c>
+      <c r="B181" s="12" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A182" s="10">
+        <v>180</v>
+      </c>
+      <c r="B182" s="12" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A183" s="10">
+        <v>181</v>
+      </c>
+      <c r="B183" s="12" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A184" s="10">
+        <v>182</v>
+      </c>
+      <c r="B184" s="12" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A185" s="10">
+        <v>183</v>
+      </c>
+      <c r="B185" s="12" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A186" s="10">
+        <v>184</v>
+      </c>
+      <c r="B186" s="12" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A187" s="10">
+        <v>185</v>
+      </c>
+      <c r="B187" s="12" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A188" s="10">
+        <v>186</v>
+      </c>
+      <c r="B188" s="12" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A189" s="10">
+        <v>187</v>
+      </c>
+      <c r="B189" s="12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A190" s="10">
+        <v>188</v>
+      </c>
+      <c r="B190" s="12" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A191" s="10">
+        <v>189</v>
+      </c>
+      <c r="B191" s="12" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A192" s="10">
+        <v>190</v>
+      </c>
+      <c r="B192" s="12" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A193" s="10">
+        <v>191</v>
+      </c>
+      <c r="B193" s="12" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A194" s="10">
+        <v>192</v>
+      </c>
+      <c r="B194" s="12" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A195" s="10">
+        <v>193</v>
+      </c>
+      <c r="B195" s="12" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A196" s="10">
+        <v>194</v>
+      </c>
+      <c r="B196" s="12" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A197" s="10">
+        <v>195</v>
+      </c>
+      <c r="B197" s="12" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A198" s="10">
+        <v>196</v>
+      </c>
+      <c r="B198" s="12" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A199" s="10">
+        <v>197</v>
+      </c>
+      <c r="B199" s="12" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A200" s="10">
+        <v>198</v>
+      </c>
+      <c r="B200" s="12" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A201" s="10">
+        <v>199</v>
+      </c>
+      <c r="B201" s="12" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A202" s="10">
+        <v>200</v>
+      </c>
+      <c r="B202" s="12" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A203" s="10">
+        <v>201</v>
+      </c>
+      <c r="B203" s="12" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A204" s="10">
+        <v>202</v>
+      </c>
+      <c r="B204" s="12" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A205" s="10">
+        <v>203</v>
+      </c>
+      <c r="B205" s="12" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A206" s="10">
+        <v>204</v>
+      </c>
+      <c r="B206" s="12" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A207" s="10">
+        <v>205</v>
+      </c>
+      <c r="B207" s="12" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A208" s="10">
+        <v>206</v>
+      </c>
+      <c r="B208" s="12" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A209" s="10">
+        <v>207</v>
+      </c>
+      <c r="B209" s="12" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A210" s="10">
+        <v>208</v>
+      </c>
+      <c r="B210" s="12" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A211" s="10">
+        <v>209</v>
+      </c>
+      <c r="B211" s="12" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A212" s="10">
+        <v>210</v>
+      </c>
+      <c r="B212" s="12" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A213" s="10">
+        <v>211</v>
+      </c>
+      <c r="B213" s="12" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A214" s="10">
+        <v>212</v>
+      </c>
+      <c r="B214" s="12" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A215" s="10">
+        <v>213</v>
+      </c>
+      <c r="B215" s="12" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A216" s="10">
+        <v>214</v>
+      </c>
+      <c r="B216" s="12" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A217" s="10">
+        <v>215</v>
+      </c>
+      <c r="B217" s="12" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A218" s="10">
+        <v>216</v>
+      </c>
+      <c r="B218" s="12" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A219" s="10">
+        <v>217</v>
+      </c>
+      <c r="B219" s="12" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A220" s="10">
+        <v>218</v>
+      </c>
+      <c r="B220" s="12" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A221" s="10">
+        <v>219</v>
+      </c>
+      <c r="B221" s="12" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A222" s="10">
+        <v>220</v>
+      </c>
+      <c r="B222" s="12" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A223" s="10">
+        <v>221</v>
+      </c>
+      <c r="B223" s="12" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A224" s="10">
+        <v>222</v>
+      </c>
+      <c r="B224" s="12" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A225" s="10">
+        <v>223</v>
+      </c>
+      <c r="B225" s="12" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A226" s="10">
+        <v>224</v>
+      </c>
+      <c r="B226" s="12" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A227" s="10">
+        <v>225</v>
+      </c>
+      <c r="B227" s="12" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A228" s="10">
+        <v>226</v>
+      </c>
+      <c r="B228" s="12" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A229" s="10">
+        <v>227</v>
+      </c>
+      <c r="B229" s="12" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A230" s="10">
+        <v>228</v>
+      </c>
+      <c r="B230" s="12" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A231" s="10">
+        <v>229</v>
+      </c>
+      <c r="B231" s="12" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A232" s="10">
+        <v>230</v>
+      </c>
+      <c r="B232" s="12" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A233" s="10">
+        <v>231</v>
+      </c>
+      <c r="B233" s="12" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A234" s="10">
+        <v>232</v>
+      </c>
+      <c r="B234" s="12" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A235" s="10">
+        <v>233</v>
+      </c>
+      <c r="B235" s="12" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A236" s="10">
+        <v>234</v>
+      </c>
+      <c r="B236" s="12" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A237" s="10">
+        <v>235</v>
+      </c>
+      <c r="B237" s="12" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A238" s="10">
+        <v>236</v>
+      </c>
+      <c r="B238" s="12" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A239" s="10">
+        <v>237</v>
+      </c>
+      <c r="B239" s="12" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A240" s="10">
+        <v>238</v>
+      </c>
+      <c r="B240" s="12" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A241" s="10">
+        <v>239</v>
+      </c>
+      <c r="B241" s="12" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A242" s="10">
+        <v>240</v>
+      </c>
+      <c r="B242" s="12" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A243" s="10">
+        <v>241</v>
+      </c>
+      <c r="B243" s="12" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A244" s="10">
+        <v>242</v>
+      </c>
+      <c r="B244" s="12" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A245" s="10">
+        <v>243</v>
+      </c>
+      <c r="B245" s="12" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A246" s="10">
+        <v>244</v>
+      </c>
+      <c r="B246" s="12" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A247" s="10">
+        <v>245</v>
+      </c>
+      <c r="B247" s="12" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A248" s="10">
+        <v>246</v>
+      </c>
+      <c r="B248" s="12" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A249" s="10">
+        <v>247</v>
+      </c>
+      <c r="B249" s="12" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A250" s="10">
+        <v>248</v>
+      </c>
+      <c r="B250" s="12" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A251" s="10">
+        <v>249</v>
+      </c>
+      <c r="B251" s="12" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A252" s="10">
+        <v>250</v>
+      </c>
+      <c r="B252" s="12" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A253" s="10">
+        <v>251</v>
+      </c>
+      <c r="B253" s="12" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A254" s="10">
+        <v>252</v>
+      </c>
+      <c r="B254" s="12" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A255" s="10">
+        <v>253</v>
+      </c>
+      <c r="B255" s="12" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A256" s="10">
+        <v>254</v>
+      </c>
+      <c r="B256" s="12" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A257" s="10">
+        <v>255</v>
+      </c>
+      <c r="B257" s="12" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A258" s="10">
+        <v>256</v>
+      </c>
+      <c r="B258" s="12" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A259" s="10">
+        <v>257</v>
+      </c>
+      <c r="B259" s="12" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A260" s="10">
+        <v>258</v>
+      </c>
+      <c r="B260" s="12" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A261" s="10">
+        <v>259</v>
+      </c>
+      <c r="B261" s="12" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A262" s="10">
+        <v>260</v>
+      </c>
+      <c r="B262" s="12" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A263" s="10">
+        <v>261</v>
+      </c>
+      <c r="B263" s="12" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A264" s="10">
+        <v>262</v>
+      </c>
+      <c r="B264" s="12" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A265" s="10">
+        <v>263</v>
+      </c>
+      <c r="B265" s="12" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A266" s="10">
+        <v>264</v>
+      </c>
+      <c r="B266" s="12" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A267" s="10">
+        <v>265</v>
+      </c>
+      <c r="B267" s="12" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A268" s="10">
+        <v>266</v>
+      </c>
+      <c r="B268" s="12" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A269" s="10">
+        <v>267</v>
+      </c>
+      <c r="B269" s="12" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A270" s="10">
+        <v>268</v>
+      </c>
+      <c r="B270" s="12" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A271" s="10">
+        <v>269</v>
+      </c>
+      <c r="B271" s="12" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A272" s="10">
+        <v>270</v>
+      </c>
+      <c r="B272" s="12" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A273" s="10">
+        <v>271</v>
+      </c>
+      <c r="B273" s="12" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A274" s="10">
+        <v>272</v>
+      </c>
+      <c r="B274" s="12" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A275" s="10">
+        <v>273</v>
+      </c>
+      <c r="B275" s="12" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A276" s="10">
+        <v>274</v>
+      </c>
+      <c r="B276" s="12" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A277" s="10">
+        <v>275</v>
+      </c>
+      <c r="B277" s="12" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A278" s="10">
+        <v>276</v>
+      </c>
+      <c r="B278" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A279" s="10">
+        <v>277</v>
+      </c>
+      <c r="B279" s="12" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A280" s="10">
+        <v>278</v>
+      </c>
+      <c r="B280" s="12" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A281" s="10">
+        <v>279</v>
+      </c>
+      <c r="B281" s="12" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A282" s="10">
+        <v>280</v>
+      </c>
+      <c r="B282" s="12" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A283" s="10">
+        <v>281</v>
+      </c>
+      <c r="B283" s="12" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A284" s="10">
+        <v>282</v>
+      </c>
+      <c r="B284" s="12" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A285" s="10">
+        <v>283</v>
+      </c>
+      <c r="B285" s="12" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A286" s="10">
+        <v>284</v>
+      </c>
+      <c r="B286" s="12" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A287" s="10">
+        <v>285</v>
+      </c>
+      <c r="B287" s="12" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A288" s="10">
+        <v>286</v>
+      </c>
+      <c r="B288" s="12" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A289" s="10">
+        <v>287</v>
+      </c>
+      <c r="B289" s="12" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A290" s="10">
+        <v>288</v>
+      </c>
+      <c r="B290" s="12" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A291" s="10">
+        <v>289</v>
+      </c>
+      <c r="B291" s="12" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A292" s="10">
+        <v>290</v>
+      </c>
+      <c r="B292" s="12" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A293" s="10">
+        <v>291</v>
+      </c>
+      <c r="B293" s="12" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A294" s="10">
+        <v>292</v>
+      </c>
+      <c r="B294" s="12" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A295" s="10">
+        <v>293</v>
+      </c>
+      <c r="B295" s="12" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A296" s="10">
+        <v>294</v>
+      </c>
+      <c r="B296" s="12" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A297" s="10">
+        <v>295</v>
+      </c>
+      <c r="B297" s="12" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A298" s="10">
+        <v>296</v>
+      </c>
+      <c r="B298" s="12" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A299" s="10">
+        <v>297</v>
+      </c>
+      <c r="B299" s="12" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A300" s="10">
+        <v>298</v>
+      </c>
+      <c r="B300" s="12" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A301" s="10">
+        <v>299</v>
+      </c>
+      <c r="B301" s="12" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A302" s="10">
+        <v>300</v>
+      </c>
+      <c r="B302" s="12" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A303" s="10">
+        <v>301</v>
+      </c>
+      <c r="B303" s="12" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A304" s="10">
+        <v>302</v>
+      </c>
+      <c r="B304" s="12" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A305" s="10">
+        <v>303</v>
+      </c>
+      <c r="B305" s="12" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A306" s="10">
+        <v>304</v>
+      </c>
+      <c r="B306" s="12" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A307" s="10">
+        <v>305</v>
+      </c>
+      <c r="B307" s="12" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A308" s="10">
+        <v>306</v>
+      </c>
+      <c r="B308" s="12" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A309" s="10">
+        <v>307</v>
+      </c>
+      <c r="B309" s="12" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A310" s="10">
+        <v>308</v>
+      </c>
+      <c r="B310" s="12" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A311" s="10">
+        <v>309</v>
+      </c>
+      <c r="B311" s="12" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A312" s="10">
+        <v>310</v>
+      </c>
+      <c r="B312" s="12" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A313" s="10">
+        <v>311</v>
+      </c>
+      <c r="B313" s="12" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A314" s="10">
+        <v>312</v>
+      </c>
+      <c r="B314" s="12" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A315" s="10">
+        <v>313</v>
+      </c>
+      <c r="B315" s="12" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A316" s="10">
+        <v>314</v>
+      </c>
+      <c r="B316" s="12" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A317" s="10">
+        <v>315</v>
+      </c>
+      <c r="B317" s="12" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A318" s="10">
+        <v>316</v>
+      </c>
+      <c r="B318" s="12" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A319" s="10">
+        <v>317</v>
+      </c>
+      <c r="B319" s="12" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A320" s="10">
+        <v>318</v>
+      </c>
+      <c r="B320" s="12" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A321" s="10">
+        <v>319</v>
+      </c>
+      <c r="B321" s="12" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A322" s="10">
+        <v>320</v>
+      </c>
+      <c r="B322" s="12" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A323" s="10">
+        <v>321</v>
+      </c>
+      <c r="B323" s="12" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A324" s="10">
+        <v>322</v>
+      </c>
+      <c r="B324" s="12" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A325" s="10">
+        <v>323</v>
+      </c>
+      <c r="B325" s="12" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A326" s="10">
+        <v>324</v>
+      </c>
+      <c r="B326" s="12" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A327" s="10">
+        <v>325</v>
+      </c>
+      <c r="B327" s="12" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A328" s="10">
+        <v>326</v>
+      </c>
+      <c r="B328" s="12" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A329" s="10">
+        <v>327</v>
+      </c>
+      <c r="B329" s="12" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A330" s="10">
+        <v>328</v>
+      </c>
+      <c r="B330" s="12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A331" s="10">
+        <v>329</v>
+      </c>
+      <c r="B331" s="12" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A332" s="10">
+        <v>330</v>
+      </c>
+      <c r="B332" s="12" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A333" s="10">
+        <v>331</v>
+      </c>
+      <c r="B333" s="12" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A334" s="10">
+        <v>332</v>
+      </c>
+      <c r="B334" s="12" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A335" s="10">
+        <v>333</v>
+      </c>
+      <c r="B335" s="12" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A336" s="10">
+        <v>334</v>
+      </c>
+      <c r="B336" s="12" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A337" s="10">
+        <v>335</v>
+      </c>
+      <c r="B337" s="12" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A338" s="10">
+        <v>336</v>
+      </c>
+      <c r="B338" s="12" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A339" s="10">
+        <v>337</v>
+      </c>
+      <c r="B339" s="12" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A340" s="10">
+        <v>338</v>
+      </c>
+      <c r="B340" s="12" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A341" s="10">
+        <v>339</v>
+      </c>
+      <c r="B341" s="12" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A342" s="10">
+        <v>340</v>
+      </c>
+      <c r="B342" s="12" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A343" s="10">
+        <v>341</v>
+      </c>
+      <c r="B343" s="12" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A344" s="10">
+        <v>342</v>
+      </c>
+      <c r="B344" s="12" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A345" s="10">
+        <v>343</v>
+      </c>
+      <c r="B345" s="12" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A346" s="10">
+        <v>344</v>
+      </c>
+      <c r="B346" s="12" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A347" s="10">
+        <v>345</v>
+      </c>
+      <c r="B347" s="12" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A348" s="10">
+        <v>346</v>
+      </c>
+      <c r="B348" s="12" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A349" s="10">
+        <v>347</v>
+      </c>
+      <c r="B349" s="12" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A350" s="10">
+        <v>348</v>
+      </c>
+      <c r="B350" s="12" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A351" s="10">
+        <v>349</v>
+      </c>
+      <c r="B351" s="12" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A352" s="10">
+        <v>350</v>
+      </c>
+      <c r="B352" s="12" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A353" s="10">
+        <v>351</v>
+      </c>
+      <c r="B353" s="12" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A354" s="10">
+        <v>352</v>
+      </c>
+      <c r="B354" s="12" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A355" s="10">
+        <v>353</v>
+      </c>
+      <c r="B355" s="12" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A356" s="10">
+        <v>354</v>
+      </c>
+      <c r="B356" s="12" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A357" s="10">
+        <v>355</v>
+      </c>
+      <c r="B357" s="12" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A358" s="10">
+        <v>356</v>
+      </c>
+      <c r="B358" s="12" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A359" s="10">
+        <v>357</v>
+      </c>
+      <c r="B359" s="12" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A360" s="10">
+        <v>358</v>
+      </c>
+      <c r="B360" s="12" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A361" s="10">
+        <v>359</v>
+      </c>
+      <c r="B361" s="12" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A362" s="10">
+        <v>360</v>
+      </c>
+      <c r="B362" s="12" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A363" s="10">
+        <v>361</v>
+      </c>
+      <c r="B363" s="12" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A364" s="10">
+        <v>362</v>
+      </c>
+      <c r="B364" s="12" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A365" s="10">
+        <v>363</v>
+      </c>
+      <c r="B365" s="12" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A366" s="10">
+        <v>364</v>
+      </c>
+      <c r="B366" s="12" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A367" s="10">
+        <v>365</v>
+      </c>
+      <c r="B367" s="12" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A368" s="10">
+        <v>366</v>
+      </c>
+      <c r="B368" s="12" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A369" s="10">
+        <v>367</v>
+      </c>
+      <c r="B369" s="12" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A370" s="10">
+        <v>368</v>
+      </c>
+      <c r="B370" s="12" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A371" s="10">
+        <v>369</v>
+      </c>
+      <c r="B371" s="12" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A372" s="10">
+        <v>370</v>
+      </c>
+      <c r="B372" s="12" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A373" s="10">
+        <v>371</v>
+      </c>
+      <c r="B373" s="12" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A374" s="10">
+        <v>372</v>
+      </c>
+      <c r="B374" s="12" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A375" s="10">
+        <v>373</v>
+      </c>
+      <c r="B375" s="12" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A376" s="10">
+        <v>374</v>
+      </c>
+      <c r="B376" s="12" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A377" s="10">
+        <v>375</v>
+      </c>
+      <c r="B377" s="12" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A378" s="10">
+        <v>376</v>
+      </c>
+      <c r="B378" s="12" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A379" s="10">
+        <v>377</v>
+      </c>
+      <c r="B379" s="12" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A380" s="10">
+        <v>378</v>
+      </c>
+      <c r="B380" s="12" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B381"/>
+    </row>
+    <row r="382" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B382"/>
+    </row>
+    <row r="383" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B383"/>
+    </row>
+    <row r="384" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B384"/>
+    </row>
+    <row r="385" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B385"/>
+    </row>
+    <row r="386" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B386"/>
+    </row>
+    <row r="387" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B387"/>
+    </row>
+    <row r="388" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B388"/>
+    </row>
+    <row r="389" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B389"/>
+    </row>
+    <row r="390" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B390"/>
+    </row>
+    <row r="391" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B391"/>
+    </row>
+    <row r="392" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B392"/>
+    </row>
+    <row r="393" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B393"/>
+    </row>
+    <row r="394" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B394"/>
+    </row>
+    <row r="395" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B395"/>
+    </row>
+    <row r="396" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B396"/>
+    </row>
+    <row r="397" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B397"/>
+    </row>
+    <row r="398" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B398"/>
+    </row>
+    <row r="399" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B399"/>
+    </row>
+    <row r="400" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B400"/>
+    </row>
+    <row r="401" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B401"/>
+    </row>
+    <row r="402" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B402"/>
+    </row>
+    <row r="403" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B403"/>
+    </row>
+    <row r="404" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B404"/>
+    </row>
+    <row r="405" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B405"/>
+    </row>
+    <row r="406" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B406"/>
+    </row>
+    <row r="407" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B407"/>
+    </row>
+    <row r="408" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B408"/>
+    </row>
+    <row r="409" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B409"/>
+    </row>
+    <row r="410" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B410"/>
+    </row>
+    <row r="411" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B411"/>
+    </row>
+    <row r="412" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B412"/>
+    </row>
+    <row r="413" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B413"/>
+    </row>
+    <row r="414" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B414"/>
+    </row>
+    <row r="415" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B415"/>
+    </row>
+    <row r="416" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B416"/>
+    </row>
+    <row r="417" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B417"/>
+    </row>
+    <row r="418" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B418"/>
+    </row>
+    <row r="419" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B419"/>
+    </row>
+    <row r="420" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B420"/>
+    </row>
+    <row r="421" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B421"/>
+    </row>
+    <row r="422" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B422"/>
+    </row>
+    <row r="423" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B423"/>
+    </row>
+    <row r="424" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B424"/>
+    </row>
+    <row r="425" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B425"/>
+    </row>
+    <row r="426" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B426"/>
+    </row>
+    <row r="427" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B427"/>
+    </row>
+    <row r="428" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B428"/>
+    </row>
+    <row r="429" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B429"/>
+    </row>
+    <row r="430" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B430"/>
+    </row>
+    <row r="431" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B431"/>
+    </row>
+    <row r="432" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B432"/>
+    </row>
+    <row r="433" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B433"/>
+    </row>
+    <row r="434" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B434"/>
+    </row>
+    <row r="435" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B435"/>
+    </row>
+    <row r="436" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B436"/>
+    </row>
+    <row r="437" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B437"/>
+    </row>
+    <row r="438" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B438"/>
+    </row>
+    <row r="439" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B439"/>
+    </row>
+    <row r="440" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B440"/>
+    </row>
+    <row r="441" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B441"/>
+    </row>
+    <row r="442" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B442"/>
+    </row>
+    <row r="443" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B443"/>
+    </row>
+    <row r="444" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B444"/>
+    </row>
+    <row r="445" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B445"/>
+    </row>
+    <row r="446" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B446"/>
+    </row>
+    <row r="447" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B447"/>
+    </row>
+    <row r="448" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B448"/>
+    </row>
+    <row r="449" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B449"/>
+    </row>
+    <row r="450" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B450"/>
+    </row>
+    <row r="451" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B451"/>
+    </row>
+    <row r="452" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B452"/>
+    </row>
+    <row r="453" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B453"/>
+    </row>
+    <row r="454" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B454"/>
+    </row>
+    <row r="455" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B455"/>
+    </row>
+    <row r="456" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B456"/>
+    </row>
+    <row r="457" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B457"/>
+    </row>
+    <row r="458" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B458"/>
+    </row>
+    <row r="459" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B459"/>
+    </row>
+    <row r="460" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B460"/>
+    </row>
+    <row r="461" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B461"/>
+    </row>
+    <row r="462" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B462"/>
+    </row>
+    <row r="463" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B463"/>
+    </row>
+    <row r="464" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B464"/>
+    </row>
+    <row r="465" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B465"/>
+    </row>
+    <row r="466" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B466"/>
+    </row>
+    <row r="467" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B467"/>
+    </row>
+    <row r="468" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B468"/>
+    </row>
+    <row r="469" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B469"/>
+    </row>
+    <row r="470" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B470"/>
+    </row>
+    <row r="471" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B471"/>
+    </row>
+    <row r="472" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B472"/>
+    </row>
+    <row r="473" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B473"/>
+    </row>
+    <row r="474" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B474"/>
+    </row>
+    <row r="475" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B475"/>
+    </row>
+    <row r="476" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B476"/>
+    </row>
+    <row r="477" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B477"/>
+    </row>
+    <row r="478" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B478"/>
+    </row>
+    <row r="479" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B479"/>
+    </row>
+    <row r="480" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B480"/>
+    </row>
+    <row r="481" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B481"/>
+    </row>
+    <row r="482" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B482"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
